--- a/data/daily/2026-10/2026-10-16.xlsx
+++ b/data/daily/2026-10/2026-10-16.xlsx
@@ -1170,14 +1170,114 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,135 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="352425" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1425,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,24 +1553,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1578,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,154 +1603,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,31 +2596,31 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16288</v>
+        <v>16289</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>우수한 체력 증진 효과 — 복용 후 체력 회복 및 건강 증진에 도움 됨</t>
+          <t>간편한 복합 영양 섭취 — 액상과 정제가 함께 들어 있어 다양한 영양소를 한 번에 간편하게 복용함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>휴대와 복용의 편리성 — 컴팩트한 크기라 하나씩 챙겨 먹기 편함</t>
+          <t>체력 보충 및 건강 관리 — 떨어진 체력을 보충하고 피로를 해소하는 데 뛰어난 효능을 체감함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>높은 선물 만족도 — 고급 비타민이라 주고받을 때 만족도가 높음</t>
+          <t>높은 선물 만족도 — 선물용으로 주고받기에 적합하며 추가 증정 혜택이 있어 만족스러움</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>증정품 누락 발생 — 안내된 추가 1개 증정 상품이 누락되어 배송됨</t>
+          <t>공복 복용 시 속 불편함 — 빈속에 섭취 시 속이 다소 불편하여 식후 복용이 권장됨</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>사전 안내 없는 일괄 배송 — 여러 주문건이 사전 문의 없이 한 번에 함께 배송됨</t>
+          <t>증정품 누락과 배송 문제 — 안내된 추가 증정품이 누락되거나 사전 안내 없는 일괄 배송이 발생함</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -2663,21 +2663,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15622</v>
+        <v>15623</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증대 — 피곤하고 체력 없을 때 복용 시 빠른 기운 회복 체감</t>
+          <t>빠른 체력 회복 효과 — 피로감이 심할 때 섭취하면 하루 종일 활력이 유지되고 기운이 남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 멀티비타민과 미네랄을 한 번에 간편히 챙기기 좋음</t>
+          <t>올인원 간편 영양 관리 — 여러 영양제를 따로 먹을 필요 없이 멀티비타민과 미네랄을 한 번에 챙김</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>높은 가성비 선물 — 배송이 빠르고 생일 선물용으로 가성비 뛰어남</t>
+          <t>높은 가성비와 선물 적합성 — 패키지가 깔끔하고 가격 대비 구성이 좋아 생일 선물로 주고받기 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2726,20 +2726,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 환절기 피로감이 줄고 하루 시작의 활력이 느껴짐</t>
+          <t>탁월한 피로 회복과 활력 — 복용 후 활력이 눈에 띄게 좋아지고 피로감이 크게 감소함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 포장이 예쁘고 따뜻한 마음을 전하기 좋음</t>
+          <t>고급스러운 포장의 선물용 — 포장이 고급스럽고 예뻐서 받는 사람의 감동이 큰 선물임</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>진한 액상 제형 — 다른 액상 비타민에 비해 농도가 진하고 양호함</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>가족이 나누어 먹는 대용량 — 30개 대용량 구성이라 온 가족이 함께 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>액상 제형의 맛 호불호 — 액상 비타민 특유의 맛은 진한 편이라 취향에 따라 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2785,22 +2789,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득해서 간식처럼 부담 없이 먹기 좋음</t>
+          <t>맛있고 쫀득한 젤리 제형 — 새콤달콤하고 쫀득한 젤리 형태라 거부감 없이 간식처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알약 대비 쉬운 섭취 — 알약에 거부감이 있는 사람도 편하게 복용 가능</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>부담 없는 선물 아이템 — 필요한 영양소를 간편히 챙길 수 있는 만족스러운 선물</t>
-        </is>
-      </c>
+          <t>편리한 복용성과 휴대성 — 알약을 잘 못 먹는 사람도 편하게 챙겨 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>일일 섭취량 제한 — 맛있어서 더 먹고 싶어도 정해진 일일 양만 먹어야 함</t>
+          <t>하루 섭취량 제한의 아쉬움 — 맛있어서 더 먹고 싶으나 하루 정해진 권장 섭취량이 제한되어 있음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261015103203_b8bc495679ff4e64935331509be98c02.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -2848,19 +2848,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>환절기 컨디션 관리 — 환절기 면력력 강화 및 피로 회복에 도움 됨</t>
+          <t>우수한 개별 휴대성 — 한 병씩 개별 포장되어 있어 출근 시나 외출할 때 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 1병 개별 포장 — 한 병씩 포장되어 출근 시 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>센스 있는 선물 구성 — 10일 구성으로 부담 없이 품질 좋은 비타민 선물 가능</t>
-        </is>
-      </c>
+          <t>컨디션 및 피로 개선 효과 — 환절기 면역력 관리와 바쁜 일상의 피로 해소에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2907,22 +2903,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>신선한 분말 액상 혼합 — 캡을 눌러 분말과 액상을 직전에 섞어 먹는 재미와 프레시함</t>
+          <t>고급스러운 포장 패키지 — 선물 상자가 고급스러워 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>고급스러운 기프트 포장 — 고급진 포장과 쇼핑백 증정으로 선물용에 최적화됨</t>
+          <t>신선하고 간편한 혼합 제형 — 캡을 눌러 분말과 액상을 섞어 마시는 방식이라 신선하고 간편함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 액상 타입이라 흡수와 효과가 빠르고 활력이 생김</t>
+          <t>즉각적인 활력 충전 효과 — 섭취 후 활력이 생기고 피로 회복 속도가 빠르게 체감됨</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>복용 시 목메임 발생 — 음용 후 약간의 목메임이 있어 물을 마셔야 함</t>
+          <t>음용 후 발생하는 목메임 — 분말과 함께 복용 시 다소 목이 메어 물을 추가로 마셔야 함</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2966,21 +2962,21 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 올인원 영양 케어 — 하루 한 병으로 21종 영양소를 알차게 챙김</t>
+          <t>21종 올인원 영양 보충 — 하루 한 병으로 21가지 비타민과 미네랄을 한 번에 섭취함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>고함량 피로 감소 효과 — 고함량 비타민 B군 덕분에 피로감이 덜하고 힘이 남</t>
+          <t>피로감 감소와 활력 증진 — 고함량 비타민 B군으로 체력이 떨어지는 환절기 피로 해소에 효과적임</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>우수한 이동 휴대성 — 외출이나 활동 시 하나씩 들고 다니며 섭취하기 편함</t>
+          <t>간편한 섭취와 높은 휴대성 — 외출이나 이동 시 들고 다니며 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3029,22 +3025,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 복용 후 확실한 파워업과 활력을 체감할 수 있음</t>
+          <t>성별 맞춤형 제품 구성 — 남성과 여성용 영양소가 구분되어 있어 맞춤 관리가 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>성별 맞춤형 선택 — 남성용과 여성용이 구분되어 맞춤 영양 관리 가능</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>특유의 쓴맛 제거 — 비타민 특유의 쓴맛이 없고 찐득하여 건강해지는 느낌</t>
-        </is>
-      </c>
+          <t>확실한 활력과 체력 증진 — 직장인 체력 보충에 효과적이며 섭취 시 활력이 돋는 것을 확연히 느낌</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 같은 맛이 나서 맛 자체는 아쉬움</t>
+          <t>감기약 맛 느낌의 호불호 — 진한 오렌지 맛이나 약 특유의 맛이 느껴져 맛에 대한 호불호가 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3092,17 +3084,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>우수한 외출 휴대성 — 한 포씩 가방에 넣어 다니며 간편하게 먹기 좋음</t>
+          <t>피로와 컨디션 빠른 회복 — 컨디션이 저하되었을 때 복용 후 숙면을 취하면 다음 날 몸이 가벼워짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>다음 날 빠른 피로 회복 — 컨디션 나쁠 때 먹고 자면 다음 날 피로가 풀림</t>
+          <t>휴대성 높은 개별 포장 — 한 포씩 포장되어 가방에 넣고 외출 시 간편하게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>부담 없는 상큼한 맛 — 맛이 부담스럽지 않아 지속적으로 챙겨 먹기 쉬움</t>
+          <t>부담 없는 무난한 맛 — 맛이 거부감 없이 무난하여 매일 꾸준히 복용하기에 용이함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3130,7 +3122,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>28,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3151,22 +3143,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>고함량 비타민C 효과 — 고용량이라 섭취 후 하루 피로감이 덜함</t>
+          <t>고용량 비타민C 함유량 — 100포 대용량의 3000mg 고함량 비타민C를 간편하게 섭취함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>새로운 가루 타입 — 분말 형태 제형이라 챙겨 먹는 재미가 있음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>선물하기 좋은 필수템 — 건강 관리용 생일 선물로 주고받기 좋음</t>
-        </is>
-      </c>
+          <t>피로 해소 체감 효과 — 복용 시 하루의 피로도가 줄어들고 컨디션 관리에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>강렬하게 신 맛 — 분말 섭취 시 신맛이 매우 강하게 느껴짐</t>
+          <t>강한 신맛으로 인한 자극 — 분말 제형의 신맛이 매우 강하여 섭취 시 놀랄 수 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3214,20 +3202,24 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>편안한 소화 촉진 — 섭취 후 소화가 잘 되고 속이 가벼워짐</t>
+          <t>속이 편해지는 소화 개선 — 섭취 후 소화가 잘 되고 몸이 한결 가벼워지는 것을 체감함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>물 없는 간편 복용 — 거부감 없는 맛으로 물 없이도 간편히 섭취함</t>
+          <t>부담 없는 맛과 편한 섭취 — 맛이 고소하고 부담 없으며 물 없이도 간편하게 복용할 수 있음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>알찬 세일 및 사은품 — 할인 특가와 증정품 구성이 알차 가성비가 높음</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>알찬 혜택과 풍부한 사은품 — 할인 행사가와 함께 저당 칩 등 풍성한 증정품을 제공받음</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>기프티콘 별도 발송 문의 — 이벤트 사은품인 기프티콘의 별도 발송 여부 확인이 필요한 경우가 있음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3269,21 +3261,21 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>속 더부룩함 완화 — 섭취 후 속 편안함과 소화 개선 효과를 느낌</t>
+          <t>편안한 속과 소화 촉진 — 매일 먹으면 속이 편안해지고 더부룩함 없이 소화가 잘 됨</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>달콤한 콘스프 맛 — 초당옥수수의 달달한 콘스프 맛이라 맛있게 먹음</t>
+          <t>고소하고 우수한 풍미 — 거부감 없이 고소하고 맛있어서 꾸준히 먹기 편함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>혜자스러운 푸짐한 사은품 — 견과류바, 칩 등 받은 증정품이 본품 이상으로 풍성함</t>
+          <t>혜자로운 구성과 증정품 — 착한 가격 대비 견과류바와 저당 단백칩 등 알찬 사은품이 넉넉함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3293,7 +3285,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3301,48 +3293,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>69</v>
+        <v>261</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>촉촉하고 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양해서 질리지 않음</t>
+          <t>뛰어난 맛과 높은 풍미 — 효소 특유의 거부감 없이 맛이 뛰어남</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>간편한 조리 및 활용 — 전자레인지에 데우기만 하면 되어 식사 대용으로 편함</t>
+          <t>고품질 굿즈 패키지 구성 — 함께 구성된 포토카드와 엽서 등 굿즈 디자인과 퀄리티가 만족스러움</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>저칼로리 식단 관리 — 칼로리가 낮아 다이어트 건강식으로 적합함</t>
+          <t>알찬 제품 구성과 포장 — 사은품이 푸짐하고 배송 포장 상태가 매우 깔끔함</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3352,7 +3344,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3360,48 +3352,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>261</v>
+        <v>69</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>거부감 없는 훌륭한 맛 — 효소임에도 맛이 좋아 부담 없이 먹기 좋음</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 소스가 다양해 질리지 않음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고품질 굿즈 증정 — 포토카드와 엽서의 퀄리티가 높아 매우 만족스러움</t>
+          <t>전자레인지 간편 조리 — 전자레인지에 데우기만 하면 바로 먹을 수 있어 조리가 단순함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>깔끔하고 알찬 패키지 — 제품 포장이 깔끔하며 구성품이 풍성함</t>
+          <t>저칼로리 및 높은 가성비 — 칼로리가 낮아 식단 관리에 좋고 저렴한 가격대로 구매 가능함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3450,22 +3442,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 플리츠백 등 에디션 포장이 예쁘고 고급스러움</t>
+          <t>고급 포장과 플리츠백 증정 — 포장 상태가 뛰어나고 플리츠백 등이 포함되어 선물용으로 탁월함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 제형 — 맛이 좋아 하루 한 병씩 꾸준히 먹기 편함</t>
+          <t>비린 맛 없는 맛있는 액상 — 콜라겐 특유의 비린 맛이 없고 상큼해서 마시기 편리함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>피로 감소 및 피부 케어 — 복용 후 피로감이 덜하고 피부 탄력 개선 기대감 상승</t>
+          <t>피로도 감소 체감 효과 — 꾸준히 복용 시 피로가 덜한 느낌을 받아 만족함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>비싼 가격대 부담 — 가격대가 높아 할인할 때만 주로 구매하게 됨</t>
+          <t>다소 높은 가격대 — 가격대가 다소 비싼 편이라 주로 할인 행사를 통해 구매하게 됨</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3513,17 +3505,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>맛있는 고단백 저당 — 비린 맛이나 텁텁함 없이 달콤하고 맛이 훌륭함</t>
+          <t>풍부한 토핑과 맛있는 식감 — 크런치볼 토핑이 가득 들어있어 씹는 재미가 있고 디저트처럼 맛있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>바삭한 토핑과 식감 — 크런치볼 토핑이 풍부하여 씹는 식감이 좋음</t>
+          <t>높은 포만감과 고단백 구성 — 단백질 20g 이상 함유로 든든하여 식사 대용으로 최적임</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>든든한 포만감 제공 — 물만 타서 먹어도 아침 식사 대용으로 속이 든든함</t>
+          <t>물만 타도 우수한 간편성 — 우유 없이 물만 넣어 흔들어 마셔도 충분히 고소하고 달콤함</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3568,21 +3560,21 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>확실한 숙취 감소 효과 — 음주 전후 섭취 시 다음 날 속이 편하고 숙취가 적음</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 속 더부룩함과 두통이 개선됨</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>우수한 휴대와 간편함 — 액상 스틱형이라 주머니에 넣고 필요할 때 바로 짜먹음</t>
+          <t>벌꿀 함유로 달콤한 맛 — 벌꿀이 들어가 거부감 없는 은은한 단맛을 제공함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>세련된 퍼플 패키지 — 보라색 포장이 고급스러워 주변 지인 선물용으로 양호함</t>
+          <t>휴대하기 편한 스틱 파우치 — 개별 스틱 형태라 가방이나 주머니에 넣고 술자리에 챙겨가기 용이함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3631,27 +3623,23 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>높은 포만감과 맛 — 맛있는 소스와 우수한 식감으로 1개만 먹어도 속이 차오름</t>
+          <t>높은 포만감과 우수한 맛 — 한 팩만으로도 배가 든든하며 소스 맛이 뛰어나 식단 관리가 쉬움</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 사은품 — 증정품으로 제공되는 가방이 디자인도 예쁘고 유용함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>가성비 좋은 구성 — 할인된 가격으로 30팩 대용량을 구매할 수 있음</t>
-        </is>
-      </c>
+          <t>예쁘고 실용적인 보냉백 — 증정되는 사은품 보냉백 디자인이 예쁘고 쓰임새가 좋음</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>다소 강한 간 — 생각보다 양념의 간이 세게 느껴짐</t>
+          <t>다소 강한 소스 간 — 단독 섭취 시 소스 간이 다소 강하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>배송 중 상품 파손 — 포장이 터져서 소스가 묻거나 비닐 포장이 헐렁함</t>
+          <t>오배송 및 비닐 포장 파손 — 구성 품목이 오배송되거나 비닐 포장이 터져 소스가 묻어나는 문제 발생</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -3667,50 +3655,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1935</v>
+        <v>218</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>우수한 물 용해성 — 물에 잘 녹아 복용하기가 매우 편리함</t>
+          <t>비린 맛 없는 음료 같은 맛 — 프로틴 특유의 텁텁함이나 비린 맛이 없고 일반 음료처럼 맛있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 퍼포먼스 향상 — 근력 증진 및 운동 기량 유지에 뛰어난 도움 됨</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>가방에 쏙 들어가는 용기 — 사이즈가 적당해 가방에 넣어 다니기 좋음</t>
-        </is>
-      </c>
+          <t>운동 후 든든한 포만감 — 운동 후 복용 시 적절한 포만감을 주어 허기짐을 달래줌</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3726,48 +3710,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>218</v>
+        <v>1937</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>특유의 비린 맛 제거 — 단백질 음료 특유의 비리고 텁텁한 맛이 전혀 없음</t>
+          <t>물에 잘 녹는 높은 용해도 — 물에 깔끔하게 잘 녹아 복용 및 음용 과정이 편리함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 맛 — 초코딸기, 모카초콜릿 등 음료수처럼 마시기 좋음</t>
+          <t>운동 수행력과 근력 강화 — 헬스 및 근력 운동 시 퍼포먼스와 근성장에 도움을 줌</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>포만감으로 간식 대체 — 마시면 배가 차서 입 심심할 때나 운동 후 먹기 적합함</t>
+          <t>휴대하기 알맞은 용기 크기 — 용기 사이즈가 적당해 운동 가방에 넣어 가지고 다니기 편함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -4019,7 +4003,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4092,10 +4076,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16288</v>
+        <v>16289</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15622</v>
+        <v>15623</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3410</v>
@@ -4110,7 +4094,7 @@
         <v>1769</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>785</v>
@@ -4130,72 +4114,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>우수한 체력 증진 효과 — 복용 후 체력 회복 및 건강 증진에 도움 됨
-휴대와 복용의 편리성 — 컴팩트한 크기라 하나씩 챙겨 먹기 편함
-높은 선물 만족도 — 고급 비타민이라 주고받을 때 만족도가 높음</t>
+          <t>간편한 복합 영양 섭취 — 액상과 정제가 함께 들어 있어 다양한 영양소를 한 번에 간편하게 복용함
+체력 보충 및 건강 관리 — 떨어진 체력을 보충하고 피로를 해소하는 데 뛰어난 효능을 체감함
+높은 선물 만족도 — 선물용으로 주고받기에 적합하며 추가 증정 혜택이 있어 만족스러움</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증대 — 피곤하고 체력 없을 때 복용 시 빠른 기운 회복 체감
-간편한 올인원 섭취 — 멀티비타민과 미네랄을 한 번에 간편히 챙기기 좋음
-높은 가성비 선물 — 배송이 빠르고 생일 선물용으로 가성비 뛰어남</t>
+          <t>빠른 체력 회복 효과 — 피로감이 심할 때 섭취하면 하루 종일 활력이 유지되고 기운이 남
+올인원 간편 영양 관리 — 여러 영양제를 따로 먹을 필요 없이 멀티비타민과 미네랄을 한 번에 챙김
+높은 가성비와 선물 적합성 — 패키지가 깔끔하고 가격 대비 구성이 좋아 생일 선물로 주고받기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 환절기 피로감이 줄고 하루 시작의 활력이 느껴짐
-고급스러운 선물용 구성 — 포장이 예쁘고 따뜻한 마음을 전하기 좋음
-진한 액상 제형 — 다른 액상 비타민에 비해 농도가 진하고 양호함</t>
+          <t>탁월한 피로 회복과 활력 — 복용 후 활력이 눈에 띄게 좋아지고 피로감이 크게 감소함
+고급스러운 포장의 선물용 — 포장이 고급스럽고 예뻐서 받는 사람의 감동이 큰 선물임
+가족이 나누어 먹는 대용량 — 30개 대용량 구성이라 온 가족이 함께 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득해서 간식처럼 부담 없이 먹기 좋음
-알약 대비 쉬운 섭취 — 알약에 거부감이 있는 사람도 편하게 복용 가능
-부담 없는 선물 아이템 — 필요한 영양소를 간편히 챙길 수 있는 만족스러운 선물</t>
+          <t>맛있고 쫀득한 젤리 제형 — 새콤달콤하고 쫀득한 젤리 형태라 거부감 없이 간식처럼 먹기 좋음
+편리한 복용성과 휴대성 — 알약을 잘 못 먹는 사람도 편하게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>환절기 컨디션 관리 — 환절기 면력력 강화 및 피로 회복에 도움 됨
-간편한 1병 개별 포장 — 한 병씩 포장되어 출근 시 챙겨 먹기 편함
-센스 있는 선물 구성 — 10일 구성으로 부담 없이 품질 좋은 비타민 선물 가능</t>
+          <t>우수한 개별 휴대성 — 한 병씩 개별 포장되어 있어 출근 시나 외출할 때 챙겨 먹기 편함
+컨디션 및 피로 개선 효과 — 환절기 면역력 관리와 바쁜 일상의 피로 해소에 도움이 됨</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>신선한 분말 액상 혼합 — 캡을 눌러 분말과 액상을 직전에 섞어 먹는 재미와 프레시함
-고급스러운 기프트 포장 — 고급진 포장과 쇼핑백 증정으로 선물용에 최적화됨
-빠른 피로 회복 체감 — 액상 타입이라 흡수와 효과가 빠르고 활력이 생김</t>
+          <t>고급스러운 포장 패키지 — 선물 상자가 고급스러워 받는 사람의 만족도가 높음
+신선하고 간편한 혼합 제형 — 캡을 눌러 분말과 액상을 섞어 마시는 방식이라 신선하고 간편함
+즉각적인 활력 충전 효과 — 섭취 후 활력이 생기고 피로 회복 속도가 빠르게 체감됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 영양 케어 — 하루 한 병으로 21종 영양소를 알차게 챙김
-고함량 피로 감소 효과 — 고함량 비타민 B군 덕분에 피로감이 덜하고 힘이 남
-우수한 이동 휴대성 — 외출이나 활동 시 하나씩 들고 다니며 섭취하기 편함</t>
+          <t>21종 올인원 영양 보충 — 하루 한 병으로 21가지 비타민과 미네랄을 한 번에 섭취함
+피로감 감소와 활력 증진 — 고함량 비타민 B군으로 체력이 떨어지는 환절기 피로 해소에 효과적임
+간편한 섭취와 높은 휴대성 — 외출이나 이동 시 들고 다니며 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 복용 후 확실한 파워업과 활력을 체감할 수 있음
-성별 맞춤형 선택 — 남성용과 여성용이 구분되어 맞춤 영양 관리 가능
-특유의 쓴맛 제거 — 비타민 특유의 쓴맛이 없고 찐득하여 건강해지는 느낌</t>
+          <t>성별 맞춤형 제품 구성 — 남성과 여성용 영양소가 구분되어 있어 맞춤 관리가 가능함
+확실한 활력과 체력 증진 — 직장인 체력 보충에 효과적이며 섭취 시 활력이 돋는 것을 확연히 느낌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>우수한 외출 휴대성 — 한 포씩 가방에 넣어 다니며 간편하게 먹기 좋음
-다음 날 빠른 피로 회복 — 컨디션 나쁠 때 먹고 자면 다음 날 피로가 풀림
-부담 없는 상큼한 맛 — 맛이 부담스럽지 않아 지속적으로 챙겨 먹기 쉬움</t>
+          <t>피로와 컨디션 빠른 회복 — 컨디션이 저하되었을 때 복용 후 숙면을 취하면 다음 날 몸이 가벼워짐
+휴대성 높은 개별 포장 — 한 포씩 포장되어 가방에 넣고 외출 시 간편하게 챙겨 먹을 수 있음
+부담 없는 무난한 맛 — 맛이 거부감 없이 무난하여 매일 꾸준히 복용하기에 용이함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 효과 — 고용량이라 섭취 후 하루 피로감이 덜함
-새로운 가루 타입 — 분말 형태 제형이라 챙겨 먹는 재미가 있음
-선물하기 좋은 필수템 — 건강 관리용 생일 선물로 주고받기 좋음</t>
+          <t>고용량 비타민C 함유량 — 100포 대용량의 3000mg 고함량 비타민C를 간편하게 섭취함
+피로 해소 체감 효과 — 복용 시 하루의 피로도가 줄어들고 컨디션 관리에 도움이 됨</t>
         </is>
       </c>
     </row>
@@ -4207,33 +4187,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>증정품 누락 발생 — 안내된 추가 1개 증정 상품이 누락되어 배송됨
-사전 안내 없는 일괄 배송 — 여러 주문건이 사전 문의 없이 한 번에 함께 배송됨</t>
+          <t>공복 복용 시 속 불편함 — 빈속에 섭취 시 속이 다소 불편하여 식후 복용이 권장됨
+증정품 누락과 배송 문제 — 안내된 추가 증정품이 누락되거나 사전 안내 없는 일괄 배송이 발생함</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>액상 제형의 맛 호불호 — 액상 비타민 특유의 맛은 진한 편이라 취향에 따라 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>일일 섭취량 제한 — 맛있어서 더 먹고 싶어도 정해진 일일 양만 먹어야 함</t>
+          <t>하루 섭취량 제한의 아쉬움 — 맛있어서 더 먹고 싶으나 하루 정해진 권장 섭취량이 제한되어 있음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>복용 시 목메임 발생 — 음용 후 약간의 목메임이 있어 물을 마셔야 함</t>
+          <t>음용 후 발생하는 목메임 — 분말과 함께 복용 시 다소 목이 메어 물을 추가로 마셔야 함</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 같은 맛이 나서 맛 자체는 아쉬움</t>
+          <t>감기약 맛 느낌의 호불호 — 진한 오렌지 맛이나 약 특유의 맛이 느껴져 맛에 대한 호불호가 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>강렬하게 신 맛 — 분말 섭취 시 신맛이 매우 강하게 느껴짐</t>
+          <t>강한 신맛으로 인한 자극 — 분말 제형의 신맛이 매우 강하여 섭취 시 놀랄 수 있음</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4274,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>28,000원</t>
         </is>
       </c>
     </row>
@@ -4443,12 +4427,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4500,14 +4484,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
@@ -4530,12 +4514,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
         </is>
       </c>
     </row>
@@ -4557,14 +4541,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
@@ -4587,12 +4571,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4627,13 @@
         <v>1730</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>69</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>261</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>755</v>
@@ -4658,16 +4642,16 @@
         <v>10</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>155</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1935</v>
+        <v>218</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>218</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4678,72 +4662,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>편안한 소화 촉진 — 섭취 후 소화가 잘 되고 속이 가벼워짐
-물 없는 간편 복용 — 거부감 없는 맛으로 물 없이도 간편히 섭취함
-알찬 세일 및 사은품 — 할인 특가와 증정품 구성이 알차 가성비가 높음</t>
+          <t>속이 편해지는 소화 개선 — 섭취 후 소화가 잘 되고 몸이 한결 가벼워지는 것을 체감함
+부담 없는 맛과 편한 섭취 — 맛이 고소하고 부담 없으며 물 없이도 간편하게 복용할 수 있음
+알찬 혜택과 풍부한 사은품 — 할인 행사가와 함께 저당 칩 등 풍성한 증정품을 제공받음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>속 더부룩함 완화 — 섭취 후 속 편안함과 소화 개선 효과를 느낌
-달콤한 콘스프 맛 — 초당옥수수의 달달한 콘스프 맛이라 맛있게 먹음
-혜자스러운 푸짐한 사은품 — 견과류바, 칩 등 받은 증정품이 본품 이상으로 풍성함</t>
+          <t>편안한 속과 소화 촉진 — 매일 먹으면 속이 편안해지고 더부룩함 없이 소화가 잘 됨
+고소하고 우수한 풍미 — 거부감 없이 고소하고 맛있어서 꾸준히 먹기 편함
+혜자로운 구성과 증정품 — 착한 가격 대비 견과류바와 저당 단백칩 등 알찬 사은품이 넉넉함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 풍부한 맛 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양해서 질리지 않음
-간편한 조리 및 활용 — 전자레인지에 데우기만 하면 되어 식사 대용으로 편함
-저칼로리 식단 관리 — 칼로리가 낮아 다이어트 건강식으로 적합함</t>
+          <t>뛰어난 맛과 높은 풍미 — 효소 특유의 거부감 없이 맛이 뛰어남
+고품질 굿즈 패키지 구성 — 함께 구성된 포토카드와 엽서 등 굿즈 디자인과 퀄리티가 만족스러움
+알찬 제품 구성과 포장 — 사은품이 푸짐하고 배송 포장 상태가 매우 깔끔함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 훌륭한 맛 — 효소임에도 맛이 좋아 부담 없이 먹기 좋음
-고품질 굿즈 증정 — 포토카드와 엽서의 퀄리티가 높아 매우 만족스러움
-깔끔하고 알찬 패키지 — 제품 포장이 깔끔하며 구성품이 풍성함</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 소스가 다양해 질리지 않음
+전자레인지 간편 조리 — 전자레인지에 데우기만 하면 바로 먹을 수 있어 조리가 단순함
+저칼로리 및 높은 가성비 — 칼로리가 낮아 식단 관리에 좋고 저렴한 가격대로 구매 가능함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 플리츠백 등 에디션 포장이 예쁘고 고급스러움
-상큼하고 맛있는 제형 — 맛이 좋아 하루 한 병씩 꾸준히 먹기 편함
-피로 감소 및 피부 케어 — 복용 후 피로감이 덜하고 피부 탄력 개선 기대감 상승</t>
+          <t>고급 포장과 플리츠백 증정 — 포장 상태가 뛰어나고 플리츠백 등이 포함되어 선물용으로 탁월함
+비린 맛 없는 맛있는 액상 — 콜라겐 특유의 비린 맛이 없고 상큼해서 마시기 편리함
+피로도 감소 체감 효과 — 꾸준히 복용 시 피로가 덜한 느낌을 받아 만족함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 고단백 저당 — 비린 맛이나 텁텁함 없이 달콤하고 맛이 훌륭함
-바삭한 토핑과 식감 — 크런치볼 토핑이 풍부하여 씹는 식감이 좋음
-든든한 포만감 제공 — 물만 타서 먹어도 아침 식사 대용으로 속이 든든함</t>
+          <t>풍부한 토핑과 맛있는 식감 — 크런치볼 토핑이 가득 들어있어 씹는 재미가 있고 디저트처럼 맛있음
+높은 포만감과 고단백 구성 — 단백질 20g 이상 함유로 든든하여 식사 대용으로 최적임
+물만 타도 우수한 간편성 — 우유 없이 물만 넣어 흔들어 마셔도 충분히 고소하고 달콤함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 감소 효과 — 음주 전후 섭취 시 다음 날 속이 편하고 숙취가 적음
-우수한 휴대와 간편함 — 액상 스틱형이라 주머니에 넣고 필요할 때 바로 짜먹음
-세련된 퍼플 패키지 — 보라색 포장이 고급스러워 주변 지인 선물용으로 양호함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 속 더부룩함과 두통이 개선됨
+벌꿀 함유로 달콤한 맛 — 벌꿀이 들어가 거부감 없는 은은한 단맛을 제공함
+휴대하기 편한 스틱 파우치 — 개별 스틱 형태라 가방이나 주머니에 넣고 술자리에 챙겨가기 용이함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>높은 포만감과 맛 — 맛있는 소스와 우수한 식감으로 1개만 먹어도 속이 차오름
-실용적인 보냉백 사은품 — 증정품으로 제공되는 가방이 디자인도 예쁘고 유용함
-가성비 좋은 구성 — 할인된 가격으로 30팩 대용량을 구매할 수 있음</t>
+          <t>높은 포만감과 우수한 맛 — 한 팩만으로도 배가 든든하며 소스 맛이 뛰어나 식단 관리가 쉬움
+예쁘고 실용적인 보냉백 — 증정되는 사은품 보냉백 디자인이 예쁘고 쓰임새가 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>우수한 물 용해성 — 물에 잘 녹아 복용하기가 매우 편리함
-운동 퍼포먼스 향상 — 근력 증진 및 운동 기량 유지에 뛰어난 도움 됨
-가방에 쏙 들어가는 용기 — 사이즈가 적당해 가방에 넣어 다니기 좋음</t>
+          <t>비린 맛 없는 음료 같은 맛 — 프로틴 특유의 텁텁함이나 비린 맛이 없고 일반 음료처럼 맛있음
+운동 후 든든한 포만감 — 운동 후 복용 시 적절한 포만감을 주어 허기짐을 달래줌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>특유의 비린 맛 제거 — 단백질 음료 특유의 비리고 텁텁한 맛이 전혀 없음
-다양하고 맛있는 맛 — 초코딸기, 모카초콜릿 등 음료수처럼 마시기 좋음
-포만감으로 간식 대체 — 마시면 배가 차서 입 심심할 때나 운동 후 먹기 적합함</t>
+          <t>물에 잘 녹는 높은 용해도 — 물에 깔끔하게 잘 녹아 복용 및 음용 과정이 편리함
+운동 수행력과 근력 강화 — 헬스 및 근력 운동 시 퍼포먼스와 근성장에 도움을 줌
+휴대하기 알맞은 용기 크기 — 용기 사이즈가 적당해 운동 가방에 넣어 가지고 다니기 편함</t>
         </is>
       </c>
     </row>
@@ -4753,21 +4735,25 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 별도 발송 문의 — 이벤트 사은품인 기프티콘의 별도 발송 여부 확인이 필요한 경우가 있음</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>비싼 가격대 부담 — 가격대가 높아 할인할 때만 주로 구매하게 됨</t>
+          <t>다소 높은 가격대 — 가격대가 다소 비싼 편이라 주로 할인 행사를 통해 구매하게 됨</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>다소 강한 간 — 생각보다 양념의 간이 세게 느껴짐
-배송 중 상품 파손 — 포장이 터져서 소스가 묻거나 비닐 포장이 헐렁함</t>
+          <t>다소 강한 소스 간 — 단독 섭취 시 소스 간이 다소 강하게 느껴질 수 있음
+오배송 및 비닐 포장 파손 — 구성 품목이 오배송되거나 비닐 포장이 터져 소스가 묻어나는 문제 발생</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4791,14 +4777,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>33,000원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
-        </is>
-      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
@@ -4821,12 +4807,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5002,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5024,58 +5010,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 컬리케일 15포 15일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157057&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260706/4dOlrrhIAJM53YybYlxV919157057_00_014dOlrrhIAJM53YybYlxV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>312</v>
+        <v>5233</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>공복 복용의 편의성 — 아침 공복에 물에 타서 간단히 마시기 양호함</t>
+          <t>다이소 매장의 구매 접근성 — 다이소 매장과 몰에서 저렴하고 간편하게 계속 재구매 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>역한 냄새와 나쁜 맛 — 맛이 없고 냄새가 역하여 섭취 시 구토감을 유발함</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>효과 체감 미흡 — 꾸준히 복용해도 별다른 효과를 느끼기 힘듦</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5083,7 +5061,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5098,39 +5076,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2908</v>
+        <v>7361</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 부담 없이 건강을 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>알약 삼킴의 편의성 — 물과 함께 삼키는 알약 정제 타입이라 먹기 편함</t>
-        </is>
-      </c>
+          <t>혈압 관리를 위한 지속 복용 — 혈압 관리 목적으로 저렴하게 지속 섭취하기에 유용함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>혈압 수치 변화 체감 부족 — 단기 복용 시 혈압 수치 변화에 대한 체감이 명확하지 않음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5138,7 +5116,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5153,43 +5131,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2633</v>
+        <v>6916</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>저렴한 합리적 가격 — 실용적인 구성과 합리적인 가격으로 재구매율 높음</t>
+          <t>5천원의 압도적 가성비 — 5,000원이라는 저렴한 가격에 마그네슘을 부담 없이 구매함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>기력 회복에 도움 — 기력 떨어지고 처질 때 복용하면 빈혈 케어에 도움 됨</t>
+          <t>눈떨림 및 다리 피로 개선 — 눈 밑 떨림 증상이 완화되고 서서 일할 때 다리 무거움이 개선됨</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>지속 복용의 어려움 — 구매해 두고 잊어버려 잘 안 먹게 됨</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5197,7 +5171,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5212,39 +5186,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3943</v>
+        <v>6750</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체지방 및 붓기 감소 — 얼굴 붓기가 빠지고 체지방 감소와 쾌변 효과를 체감함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>부담 없는 5千원 가격 — 5,000원에 한 달 분량을 구매할 수 있어 가성비 우수함</t>
-        </is>
-      </c>
+          <t>믿을 수 있는 제약사 품질 — 유명 제약사 브랜드라 신뢰할 수 있으며 한 달 분량 가격이 착함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>즉각적인 효능 체감 부족 — 복용 후 단기적으로 즉각적인 효능을 느끼기는 다소 어려움</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5252,54 +5226,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 눈피로엔 아이포커스 미니 20캡슐</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982832&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/eUpKnXlsDmWUTHaFdSd5611982832_00_00eUpKnXlsDmWUTHaFdSd5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>222</v>
+        <v>1504</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>아스타잔틴 성분 함유 — 눈 건강에 도움 되는 성분이 들어있어 약사 평도 양호함</t>
+          <t>하루 한 알 간편 혈당 관리 — 하루 한 알 섭취로 식후 혈당과 체지방을 동시에 관리함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>신속 정확한 배송 — 주문 후 빠르게 배송되어 만족스러움</t>
+          <t>부담 없는 알약 크기 — 알약 크기가 작아 목넘김 시 부담 없이 꾸준히 복용 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 꾸준히 복용해도 사람에 따라 효과 체감에 시간이 걸릴 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5307,62 +5285,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1699</v>
+        <v>355</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>다양한 음용 및 요리 활용 — 물에 타 먹거나 요리용으로 쓰기 편리함</t>
+          <t>고함량 비타민D 소포장 — 4000IU 고함량 제품을 10일분 소용량 단위로 저렴하게 구함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>진한 레몬 향과 맛 — 맛이 연하지 않고 향이 살아있어 품질 양호함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>휴대성 높은 비상용 — 여행이나 외출 시 비상용으로 챙겨 다니기 좋음</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>매우 강한 신맛 — 신맛이 강렬하여 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+          <t>다이소 매장 간편 구매 — 가까운 다이소에서 손쉽게 구매해 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5370,43 +5340,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3664</v>
+        <v>2908</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>외출 시 뛰어난 휴대성 — 5포 소포장이라 여행이나 외출 시 갖고 다니기 편함</t>
+          <t>부담 없는 저렴한 가성비 — 매우 저렴한 가격으로 매일 건강을 챙길 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>물 필요 없는 짜먹는 타입 — 물 없이 어디서나 짜먹을 수 있어 소화 안 될 때 편리함</t>
+          <t>물로 삼키는 편한 정제 — 신맛 부담 없이 물과 함께 알약 형태로 꿀꺽 삼키기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5425,12 +5395,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>락피도 티니핑 칼슘스틱 12포 12일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5440,32 +5410,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817118&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/jfFr3tgA4ryuIvnhGsc5951817118_00_01jfFr3tgA4ryuIvnhGsc5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>4094</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>아이들의 높은 기호도 — 인기 캐릭터 패키지로 아이가 사달라고 하며 잘 먹음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>성분 대비 착한 가격 — 가격과 성분이 모두 만족스러움</t>
-        </is>
-      </c>
+          <t>부담 없는 간 건강 관리 — 간 건강을 위해 저렴한 가격으로 지속해서 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>가격 인하에 대한 아쉬움 — 다른 품목 대비 가격이 조금 더 저렴해졌으면 하는 아쉬움이 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5480,12 +5450,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5495,39 +5465,43 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1435</v>
+        <v>1747</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>맛있는 포도 젤리 맛 — 블루베리 및 포도 맛 젤리라 습관처럼 매일 먹기 편함</t>
+          <t>비린내 없는 상큼한 맛 — 식물성 오메가3라 어류 비린내가 나지 않고 레몬 향이 남</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 눈 건강을 관리할 수 있음</t>
+          <t>검증된 원료 사용의 신뢰 — 유명 원료사인 DSM의 식물성 오메가3 원료를 사용하여 안심됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>직접적인 효능 체감 부족 — 단기간 복용으로는 효능 체감이 다소 불명확할 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5535,12 +5509,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5550,41 +5524,33 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591555314&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260428/PgvB4Sjc4dtxAp5jXpwI591555314_00_01PgvB4Sjc4dtxAp5jXpwI.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>404</v>
+        <v>1179</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>신속하고 확실한 장 반응 — 복용 후 몇 시간 내에 뱃속을 시원하게 비워줌</t>
+          <t>복합 영양소 함유 — 루테인지아잔틴 외에 다른 영양 성분이 함께 들어있어 알참</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>거부감 없는 요구르트 향 — 요구르트 맛이라 복용 시 거북함이 없음</t>
+          <t>작은 캡슐 크기와 목넘김 — 캡슐 알약 크기가 작아서 목넘김이 용이함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>지나치게 강한 단맛 — 맛이 너무 달아서 섭취 시 헛구역질이 나기도 함</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>복통 및 묽은 변 유발 — 섭취 후 며칠간 심한 복통과 묽은 변으로 일상에 불편함 유발</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5698,44 +5664,44 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
@@ -5743,7 +5709,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5721,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5775,32 +5741,32 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>안국약품</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
         </is>
       </c>
     </row>
@@ -5812,52 +5778,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 컬리케일 15포 15일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 철분 30정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>안국약품 토비콤 눈피로엔 아이포커스 미니 20캡슐</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>락피도 티니핑 칼슘스틱 12포 12일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5834,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5880,7 +5846,7 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5889,13 +5855,13 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5905,37 +5871,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>312</v>
+        <v>5233</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>7361</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6916</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>2908</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>2633</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>3943</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1699</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>3664</v>
-      </c>
       <c r="J7" s="3" t="n">
-        <v>354</v>
+        <v>4094</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1435</v>
+        <v>1747</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5943,99 +5909,97 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>공복 복용의 편의성 — 아침 공복에 물에 타서 간단히 마시기 양호함</t>
+          <t>다이소 매장의 구매 접근성 — 다이소 매장과 몰에서 저렴하고 간편하게 계속 재구매 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 부담 없이 건강을 챙기기 좋음
-알약 삼킴의 편의성 — 물과 함께 삼키는 알약 정제 타입이라 먹기 편함</t>
+          <t>혈압 관리를 위한 지속 복용 — 혈압 관리 목적으로 저렴하게 지속 섭취하기에 유용함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 합리적 가격 — 실용적인 구성과 합리적인 가격으로 재구매율 높음
-기력 회복에 도움 — 기력 떨어지고 처질 때 복용하면 빈혈 케어에 도움 됨</t>
+          <t>5천원의 압도적 가성비 — 5,000원이라는 저렴한 가격에 마그네슘을 부담 없이 구매함
+눈떨림 및 다리 피로 개선 — 눈 밑 떨림 증상이 완화되고 서서 일할 때 다리 무거움이 개선됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체지방 및 붓기 감소 — 얼굴 붓기가 빠지고 체지방 감소와 쾌변 효과를 체감함
-부담 없는 5千원 가격 — 5,000원에 한 달 분량을 구매할 수 있어 가성비 우수함</t>
+          <t>믿을 수 있는 제약사 품질 — 유명 제약사 브랜드라 신뢰할 수 있으며 한 달 분량 가격이 착함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>아스타잔틴 성분 함유 — 눈 건강에 도움 되는 성분이 들어있어 약사 평도 양호함
-신속 정확한 배송 — 주문 후 빠르게 배송되어 만족스러움</t>
+          <t>하루 한 알 간편 혈당 관리 — 하루 한 알 섭취로 식후 혈당과 체지방을 동시에 관리함
+부담 없는 알약 크기 — 알약 크기가 작아 목넘김 시 부담 없이 꾸준히 복용 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>다양한 음용 및 요리 활용 — 물에 타 먹거나 요리용으로 쓰기 편리함
-진한 레몬 향과 맛 — 맛이 연하지 않고 향이 살아있어 품질 양호함
-휴대성 높은 비상용 — 여행이나 외출 시 비상용으로 챙겨 다니기 좋음</t>
+          <t>고함량 비타민D 소포장 — 4000IU 고함량 제품을 10일분 소용량 단위로 저렴하게 구함
+다이소 매장 간편 구매 — 가까운 다이소에서 손쉽게 구매해 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>외출 시 뛰어난 휴대성 — 5포 소포장이라 여행이나 외출 시 갖고 다니기 편함
-물 필요 없는 짜먹는 타입 — 물 없이 어디서나 짜먹을 수 있어 소화 안 될 때 편리함</t>
+          <t>부담 없는 저렴한 가성비 — 매우 저렴한 가격으로 매일 건강을 챙길 수 있어 만족스러움
+물로 삼키는 편한 정제 — 신맛 부담 없이 물과 함께 알약 형태로 꿀꺽 삼키기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>아이들의 높은 기호도 — 인기 캐릭터 패키지로 아이가 사달라고 하며 잘 먹음
-성분 대비 착한 가격 — 가격과 성분이 모두 만족스러움</t>
+          <t>부담 없는 간 건강 관리 — 간 건강을 위해 저렴한 가격으로 지속해서 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 포도 젤리 맛 — 블루베리 및 포도 맛 젤리라 습관처럼 매일 먹기 편함
-뛰어난 가성비 — 저렴한 가격으로 부담 없이 눈 건강을 관리할 수 있음</t>
+          <t>비린내 없는 상큼한 맛 — 식물성 오메가3라 어류 비린내가 나지 않고 레몬 향이 남
+검증된 원료 사용의 신뢰 — 유명 원료사인 DSM의 식물성 오메가3 원료를 사용하여 안심됨</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>신속하고 확실한 장 반응 — 복용 후 몇 시간 내에 뱃속을 시원하게 비워줌
-거부감 없는 요구르트 향 — 요구르트 맛이라 복용 시 거북함이 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>복합 영양소 함유 — 루테인지아잔틴 외에 다른 영양 성분이 함께 들어있어 알참
+작은 캡슐 크기와 목넘김 — 캡슐 알약 크기가 작아서 목넘김이 용이함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>역한 냄새와 나쁜 맛 — 맛이 없고 냄새가 역하여 섭취 시 구토감을 유발함
-효과 체감 미흡 — 꾸준히 복용해도 별다른 효과를 느끼기 힘듦</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>지속 복용의 어려움 — 구매해 두고 잊어버려 잘 안 먹게 됨</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>매우 강한 신맛 — 신맛이 강렬하여 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>혈압 수치 변화 체감 부족 — 단기 복용 시 혈압 수치 변화에 대한 체감이 명확하지 않음</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>즉각적인 효능 체감 부족 — 복용 후 단기적으로 즉각적인 효능을 느끼기는 다소 어려움</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 꾸준히 복용해도 사람에 따라 효과 체감에 시간이 걸릴 수 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>지나치게 강한 단맛 — 맛이 너무 달아서 섭취 시 헛구역질이 나기도 함
-복통 및 묽은 변 유발 — 섭취 후 며칠간 심한 복통과 묽은 변으로 일상에 불편함 유발</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>가격 인하에 대한 아쉬움 — 다른 품목 대비 가격이 조금 더 저렴해졌으면 하는 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>직접적인 효능 체감 부족 — 단기간 복용으로는 효능 체감이 다소 불명확할 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6045,37 +6009,37 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -6277,27 +6241,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[10/16 하루특가] 닥터아돌 프로폴리스아연C 120캡슐 (60일분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218091&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021809122ko.png?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6355,7 +6319,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6363,27 +6327,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888832ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6398,7 +6362,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6406,27 +6370,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6449,27 +6413,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6484,7 +6448,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6492,31 +6456,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22694</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6558,22 +6526,10 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>615</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>이중 기능성 다이어트 케어 — 장 건강과 체지방 감소를 한 번에 관리할 수 있음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -6582,7 +6538,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6590,31 +6546,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>599</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6625,7 +6585,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6633,33 +6593,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>29,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888832ko.png?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>간식 같은 맛과 편한 복용 — 물 없이 톡 털어먹는 스틱 형태로 간식처럼 맛있게 섭취함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>간편한 이너뷰티 루틴 — 매일 꾸준히 지속하기 쉬운 이너뷰티 피부 관리 루틴임</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -6668,7 +6636,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6676,47 +6644,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587422ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17598</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있는 구미 간식 제형 — 새콤달콤해서 영양제를 안 먹는 아이도 잘 챙겨 먹음</t>
+          <t>원활한 배변 및 붓기 관리 — 과식 후 섭취 시 배변 활동이 원활해지고 뱃살 및 붓기 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>간편한 영양 보충 — 비타민과 철분 등을 구미 형태로 간편히 섭취함</t>
+          <t>귀여운 컬래버 패키지 — 인기 캐릭터와 협업한 디자인이 귀엽고 젤리 맛도 훌륭함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>재구매 유인 부족 — 개인 성향에 따라 손이 잘 가지 않아 재구매로 이어지지 않음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6841,42 +6809,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6888,52 +6856,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>닥터아돌</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>생활약속</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>비비랩</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
         </is>
       </c>
     </row>
@@ -6945,52 +6913,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[10/16 하루특가] 닥터아돌 프로폴리스아연C 120캡슐 (60일분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -7005,13 +6973,17 @@
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7024,13 +6996,17 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>615</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>22694</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>599</v>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>17598</v>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -7044,18 +7020,18 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>이중 기능성 다이어트 케어 — 장 건강과 체지방 감소를 한 번에 관리할 수 있음
-상큼한 요거트 맛 — 상큼한 요거트 맛이라 하루 한 포씩 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>간식 같은 맛과 편한 복용 — 물 없이 톡 털어먹는 스틱 형태로 간식처럼 맛있게 섭취함
+간편한 이너뷰티 루틴 — 매일 꾸준히 지속하기 쉬운 이너뷰티 피부 관리 루틴임</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 간식 제형 — 새콤달콤해서 영양제를 안 먹는 아이도 잘 챙겨 먹음
-간편한 영양 보충 — 비타민과 철분 등을 구미 형태로 간편히 섭취함</t>
+          <t>원활한 배변 및 붓기 관리 — 과식 후 섭취 시 배변 활동이 원활해지고 뱃살 및 붓기 관리에 도움 됨
+귀여운 컬래버 패키지 — 인기 캐릭터와 협업한 디자인이 귀엽고 젤리 맛도 훌륭함</t>
         </is>
       </c>
     </row>
@@ -7074,11 +7050,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>재구매 유인 부족 — 개인 성향에 따라 손이 잘 가지 않아 재구매로 이어지지 않음</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7088,52 +7060,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>16,200원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>29,800원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>18,800원</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7259,42 +7231,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>22.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -7325,20 +7297,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -7347,7 +7319,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7360,45 +7332,45 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -7407,13 +7379,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7429,6 +7401,72 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
